--- a/data/Terre di Pedemonte/investment_decision/Verscio_MFH_2005-2014_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Verscio_MFH_2005-2014_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>8.26430154545479</v>
+        <v>3.755751178711836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>1183.110824790017</v>
       </c>
       <c r="F2" t="n">
-        <v>8.967550615870357</v>
+        <v>3.755751178711834</v>
       </c>
       <c r="G2" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="H2" t="n">
-        <v>8.279485062361646</v>
+        <v>3.755751178711836</v>
       </c>
       <c r="I2" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="J2" t="n">
-        <v>8.967580283339064</v>
+        <v>3.755751178711839</v>
       </c>
       <c r="K2" t="n">
         <v>1183.110824790017</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>8.26430154545479</v>
+        <v>3.755751178711836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>1183.110824790017</v>
       </c>
       <c r="F3" t="n">
-        <v>8.967550615870357</v>
+        <v>3.755751178711834</v>
       </c>
       <c r="G3" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="H3" t="n">
-        <v>8.279485062361646</v>
+        <v>3.755751178711836</v>
       </c>
       <c r="I3" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="J3" t="n">
-        <v>8.967580283339064</v>
+        <v>3.755751178711839</v>
       </c>
       <c r="K3" t="n">
         <v>1183.110824790017</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>8.26430154545479</v>
+        <v>3.755751178711836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>1183.110824790017</v>
       </c>
       <c r="F4" t="n">
-        <v>8.967550615870357</v>
+        <v>3.755751178711834</v>
       </c>
       <c r="G4" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="H4" t="n">
-        <v>8.279485062361646</v>
+        <v>3.755751178711836</v>
       </c>
       <c r="I4" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="J4" t="n">
-        <v>8.967580283339064</v>
+        <v>3.755751178711838</v>
       </c>
       <c r="K4" t="n">
         <v>1183.110824790017</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>8.26430154545479</v>
+        <v>4.644653088958952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>1183.110824790017</v>
       </c>
       <c r="F5" t="n">
-        <v>9.223008444897825</v>
+        <v>4.611012628915441</v>
       </c>
       <c r="G5" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="H5" t="n">
-        <v>8.279485062361646</v>
+        <v>4.580638096528523</v>
       </c>
       <c r="I5" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="J5" t="n">
-        <v>9.223008444897825</v>
+        <v>4.600733756250846</v>
       </c>
       <c r="K5" t="n">
         <v>1183.110824790017</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>8.26430154545479</v>
+        <v>4.668654392346135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>1183.110824790017</v>
       </c>
       <c r="F6" t="n">
-        <v>9.223008444897825</v>
+        <v>4.638908570515608</v>
       </c>
       <c r="G6" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="H6" t="n">
-        <v>8.279485062361646</v>
+        <v>4.702732713073449</v>
       </c>
       <c r="I6" t="n">
         <v>1183.110824790017</v>
       </c>
       <c r="J6" t="n">
-        <v>9.223008444897825</v>
+        <v>4.708852888766383</v>
       </c>
       <c r="K6" t="n">
         <v>1183.110824790017</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>1.774666237185026</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.01060052866907</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.774666237185026</v>
+        <v>2.573458613471921</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.01060052866907</v>
+        <v>2.573458613471921</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>1.774666237185026</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.23018800688055</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.774666237185026</v>
+        <v>3.132630384298253</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.23018800688055</v>
+        <v>3.132630384298253</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>1.774666237185026</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.320137660141242</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.774666237185026</v>
+        <v>3.361684004790016</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.320137660141242</v>
+        <v>3.361684004790016</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>1.774666237185026</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.368219866179101</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.774666237185026</v>
+        <v>3.48412364713398</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.368219866179101</v>
+        <v>3.48412364713398</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>1.774666237185026</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.398265044995541</v>
+        <v>4.519124999999999</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.774666237185026</v>
+        <v>3.560632635626495</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.398265044995541</v>
+        <v>3.560632635626495</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.000754562731764706</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0007871809164612696</v>
+        <v>0.0005318996460949976</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000754562731764706</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0007873698070588235</v>
+        <v>0.0005265577076918817</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.000754562731764706</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0007871809164612696</v>
+        <v>0.0005318996460949976</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0007545627317647059</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0007873698070588235</v>
+        <v>0.0005265577076918817</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.000754562731764706</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0007871809164612696</v>
+        <v>0.0005318996460949976</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000754562731764706</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0007873698070588235</v>
+        <v>0.0005265577076918817</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0007545627317647075</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0007873698070588235</v>
+        <v>0.0005318996460949976</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.000754562731764706</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0007873698070588235</v>
+        <v>0.0005265577076918817</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0007545627317647059</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0008466019380792202</v>
+        <v>0.0005318996460949976</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0007545627317647574</v>
+        <v>0.0005249132047058824</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0008466019380792202</v>
+        <v>0.0005265577076918817</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01394300699999998</v>
+        <v>0.01904438265319218</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01047732487599011</v>
+        <v>0.01941273185134049</v>
       </c>
       <c r="G17" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01394300699999998</v>
+        <v>0.01923384057618853</v>
       </c>
       <c r="I17" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01047732487599011</v>
+        <v>0.01884515089600942</v>
       </c>
       <c r="K17" t="n">
         <v>0.1171212588</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.09062954549999998</v>
+        <v>0.05583536234368219</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09062954549999998</v>
+        <v>0.05577202799999998</v>
       </c>
       <c r="G18" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H18" t="n">
-        <v>0.09062954549999998</v>
+        <v>0.05060560632618853</v>
       </c>
       <c r="I18" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J18" t="n">
-        <v>0.09062954549999998</v>
+        <v>0.04984610048357074</v>
       </c>
       <c r="K18" t="n">
         <v>0.1171212588</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09062954549999998</v>
+        <v>0.05583536234368219</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09062954549999998</v>
+        <v>0.05577202799999998</v>
       </c>
       <c r="G19" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09062954549999998</v>
+        <v>0.05060560632618853</v>
       </c>
       <c r="I19" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09062954549999998</v>
+        <v>0.04984610048357074</v>
       </c>
       <c r="K19" t="n">
         <v>0.1171212588</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0766865385</v>
+        <v>0.03679097969049001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08015222062400987</v>
+        <v>0.03635929614865949</v>
       </c>
       <c r="G20" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0766865385</v>
+        <v>0.03137176575</v>
       </c>
       <c r="I20" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08015222062400987</v>
+        <v>0.03100094958756132</v>
       </c>
       <c r="K20" t="n">
         <v>0.1171212588</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01394300699999999</v>
+        <v>0.01241801978104714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F21" t="n">
-        <v>0.004163841329082852</v>
+        <v>0.01252383782710536</v>
       </c>
       <c r="G21" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01394300699999451</v>
+        <v>0.006891005927153685</v>
       </c>
       <c r="I21" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J21" t="n">
-        <v>0.004163841329082852</v>
+        <v>0.0068749605910775</v>
       </c>
       <c r="K21" t="n">
         <v>0.1171212588</v>
@@ -1420,7 +1420,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.0309978055505548</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1434,19 +1434,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.03062945635240648</v>
       </c>
       <c r="G27" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.03080834762755846</v>
       </c>
       <c r="I27" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.03119703730773755</v>
       </c>
       <c r="K27" t="n">
         <v>0.1171212588</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.03479418315631778</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.0348575175</v>
       </c>
       <c r="G28" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.04002393917381145</v>
       </c>
       <c r="I28" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.04078344501642923</v>
       </c>
       <c r="K28" t="n">
         <v>0.1171212588</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.03479418315631778</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.0348575175</v>
       </c>
       <c r="G29" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.04119005719894147</v>
       </c>
       <c r="I29" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.04119005719894146</v>
       </c>
       <c r="K29" t="n">
         <v>0.1171212588</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.03320101108645239</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.03335573885134051</v>
       </c>
       <c r="G30" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.03834326925</v>
       </c>
       <c r="I30" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.03834326925</v>
       </c>
       <c r="K30" t="n">
         <v>0.1171212588</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.0348575175</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.1171212588</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.0348575175</v>
       </c>
       <c r="G31" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.03857355548805708</v>
       </c>
       <c r="I31" t="n">
         <v>0.1171212588</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.03856234965810697</v>
       </c>
       <c r="K31" t="n">
         <v>0.1171212588</v>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>0.8564611343241482</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>0.4965975496156966</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.8564611343241482</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>0.8564611343241482</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.6037822367624375</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.8564611343241482</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>0.8564611343241482</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>0.6479238914361057</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.8564611343241482</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>0.8564611343241482</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>0.671852271402227</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.8564611343241482</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>0.8564611343241482</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>0.6870588163498706</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.8564611343241482</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.07272765267886699</v>
+        <v>0.06876407672332097</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2174,19 +2174,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07308410889968436</v>
+        <v>0.07034491095418538</v>
       </c>
       <c r="G47" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="H47" t="n">
-        <v>0.07918108191948195</v>
+        <v>0.06876407672332095</v>
       </c>
       <c r="I47" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J47" t="n">
-        <v>0.07924652181554495</v>
+        <v>0.07030924203244372</v>
       </c>
       <c r="K47" t="n">
         <v>0.352197393106352</v>
@@ -2197,7 +2197,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.07272765267886699</v>
+        <v>0.06876407672332097</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07308410889968436</v>
+        <v>0.07034491095418538</v>
       </c>
       <c r="G48" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="H48" t="n">
-        <v>0.07918108191948195</v>
+        <v>0.06876407672332095</v>
       </c>
       <c r="I48" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J48" t="n">
-        <v>0.07924652181554495</v>
+        <v>0.07030924203244372</v>
       </c>
       <c r="K48" t="n">
         <v>0.352197393106352</v>
@@ -2234,7 +2234,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.07272765267886699</v>
+        <v>0.06876407672332097</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2248,19 +2248,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F49" t="n">
-        <v>0.07308410889968436</v>
+        <v>0.07034491095418538</v>
       </c>
       <c r="G49" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="H49" t="n">
-        <v>0.07918108191948195</v>
+        <v>0.06876407672332095</v>
       </c>
       <c r="I49" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J49" t="n">
-        <v>0.07924652181554495</v>
+        <v>0.07030924203244372</v>
       </c>
       <c r="K49" t="n">
         <v>0.352197393106352</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.07371301650694784</v>
+        <v>0.07834683252365034</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1002774662551898</v>
+        <v>0.07381251501239178</v>
       </c>
       <c r="G52" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.07581850814611642</v>
+      </c>
+      <c r="I52" t="n">
         <v>0.1105036712547606</v>
       </c>
-      <c r="H52" t="n">
-        <v>0.06767639105258616</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.352197393106352</v>
-      </c>
       <c r="J52" t="n">
-        <v>0.09544096015507555</v>
+        <v>0.06980849190366226</v>
       </c>
       <c r="K52" t="n">
         <v>0.1105036712547606</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.07371301650694784</v>
+        <v>0.07834683252365034</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1002774662551898</v>
+        <v>0.07381251501239178</v>
       </c>
       <c r="G53" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.07581850814611642</v>
+      </c>
+      <c r="I53" t="n">
         <v>0.1453657171379983</v>
       </c>
-      <c r="H53" t="n">
-        <v>0.06767639105258616</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.352197393106352</v>
-      </c>
       <c r="J53" t="n">
-        <v>0.09544096015507555</v>
+        <v>0.06980849190366226</v>
       </c>
       <c r="K53" t="n">
         <v>0.1453657171379983</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.07371301650694784</v>
+        <v>0.07834683252365034</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1002774662551898</v>
+        <v>0.07381251501239178</v>
       </c>
       <c r="G54" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.07581850814611642</v>
+      </c>
+      <c r="I54" t="n">
         <v>0.1609019605082419</v>
       </c>
-      <c r="H54" t="n">
-        <v>0.06767639105258616</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.352197393106352</v>
-      </c>
       <c r="J54" t="n">
-        <v>0.09544096015507555</v>
+        <v>0.06980849190366226</v>
       </c>
       <c r="K54" t="n">
         <v>0.1609019605082419</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.08951004212282264</v>
+        <v>0.09275851119045078</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0892903025529528</v>
+        <v>0.0886899363954185</v>
       </c>
       <c r="G55" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.09314571365537337</v>
+      </c>
+      <c r="I55" t="n">
         <v>0.1692865336929988</v>
       </c>
-      <c r="H55" t="n">
-        <v>0.08578161062104156</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.352197393106352</v>
-      </c>
       <c r="J55" t="n">
-        <v>0.08578161062104157</v>
+        <v>0.08839259947056162</v>
       </c>
       <c r="K55" t="n">
         <v>0.1692865336929988</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.08951004212282264</v>
+        <v>0.09275851119045078</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0892903025529528</v>
+        <v>0.0886899363954185</v>
       </c>
       <c r="G56" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.09314571365537337</v>
+      </c>
+      <c r="I56" t="n">
         <v>0.1744623844105797</v>
       </c>
-      <c r="H56" t="n">
-        <v>0.08578161062104156</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.352197393106352</v>
-      </c>
       <c r="J56" t="n">
-        <v>0.08578161062104157</v>
+        <v>0.08839259947056162</v>
       </c>
       <c r="K56" t="n">
         <v>0.1744623844105797</v>
@@ -2547,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>0.1105036712547606</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.352197393106352</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2584,13 +2584,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>0.1453657171379983</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.352197393106352</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2621,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.1609019605082419</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.352197393106352</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.1692865336929988</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.352197393106352</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>0.352197393106352</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>0.1744623844105797</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.352197393106352</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.03723313967915492</v>
+        <v>0.02326694010486451</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F62" t="n">
-        <v>0.03566950072358691</v>
+        <v>0.02432317492317664</v>
       </c>
       <c r="G62" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="H62" t="n">
-        <v>0.03666588749074506</v>
+        <v>0.02326694010486452</v>
       </c>
       <c r="I62" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03434345484158104</v>
+        <v>0.02424807057553263</v>
       </c>
       <c r="K62" t="n">
         <v>0.352197393106352</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.03723313967915492</v>
+        <v>0.02326694010486451</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03566950072358691</v>
+        <v>0.02432317492317664</v>
       </c>
       <c r="G63" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="H63" t="n">
-        <v>0.03666588749074506</v>
+        <v>0.02326694010486452</v>
       </c>
       <c r="I63" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J63" t="n">
-        <v>0.03434345484158104</v>
+        <v>0.02424807057553263</v>
       </c>
       <c r="K63" t="n">
         <v>0.352197393106352</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.03723313967915492</v>
+        <v>0.02326694010486451</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F64" t="n">
-        <v>0.03566950072358691</v>
+        <v>0.02432317492317664</v>
       </c>
       <c r="G64" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="H64" t="n">
-        <v>0.03666588749074506</v>
+        <v>0.02326694010486452</v>
       </c>
       <c r="I64" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03434345484158104</v>
+        <v>0.02424807057553263</v>
       </c>
       <c r="K64" t="n">
         <v>0.352197393106352</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.07228207522495217</v>
+        <v>0.03367297728598118</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F65" t="n">
-        <v>0.06800787620368277</v>
+        <v>0.03788921111171511</v>
       </c>
       <c r="G65" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="H65" t="n">
-        <v>0.07593933399123234</v>
+        <v>0.03410718498536373</v>
       </c>
       <c r="I65" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J65" t="n">
-        <v>0.071516568135594</v>
+        <v>0.03874113535045768</v>
       </c>
       <c r="K65" t="n">
         <v>0.352197393106352</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.07228207522495217</v>
+        <v>0.03367297728598118</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F66" t="n">
-        <v>0.06800787620368277</v>
+        <v>0.03788921111171511</v>
       </c>
       <c r="G66" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="H66" t="n">
-        <v>0.07593933399123234</v>
+        <v>0.03410718498536373</v>
       </c>
       <c r="I66" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J66" t="n">
-        <v>0.071516568135594</v>
+        <v>0.03874113535045768</v>
       </c>
       <c r="K66" t="n">
         <v>0.352197393106352</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.01090016830628673</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.01090016830628673</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="73">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01688165939220138</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.01688165939220138</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="74">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.02082505302908974</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.02082505302908974</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="75">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.02369655494672001</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.02369655494672001</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="76">
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.02591931949178034</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02591931949178034</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.04254466088030836</v>
+        <v>0.0408909068898422</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,22 +3284,22 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F77" t="n">
-        <v>0.01389091384924405</v>
+        <v>0.04278815535192422</v>
       </c>
       <c r="G77" t="n">
-        <v>0.01090016830628673</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H77" t="n">
-        <v>0.04262393654696408</v>
+        <v>0.04341923126737612</v>
       </c>
       <c r="I77" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J77" t="n">
-        <v>0.01389091384924405</v>
+        <v>0.04690295173003938</v>
       </c>
       <c r="K77" t="n">
-        <v>0.01090016830628673</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.04254466088030836</v>
+        <v>0.0408909068898422</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01389091384924405</v>
+        <v>0.04278815535192422</v>
       </c>
       <c r="G78" t="n">
-        <v>0.01688165939220138</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H78" t="n">
-        <v>0.04262393654696408</v>
+        <v>0.04341923126737612</v>
       </c>
       <c r="I78" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01389091384924405</v>
+        <v>0.04690295173003938</v>
       </c>
       <c r="K78" t="n">
-        <v>0.01688165939220138</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.04254466088030836</v>
+        <v>0.0408909068898422</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,22 +3358,22 @@
         <v>0.352197393106352</v>
       </c>
       <c r="F79" t="n">
-        <v>0.01389091384924405</v>
+        <v>0.04278815535192422</v>
       </c>
       <c r="G79" t="n">
-        <v>0.02082505302908974</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H79" t="n">
-        <v>0.04262393654696408</v>
+        <v>0.04341923126737612</v>
       </c>
       <c r="I79" t="n">
         <v>0.352197393106352</v>
       </c>
       <c r="J79" t="n">
-        <v>0.01389091384924405</v>
+        <v>0.04690295173003938</v>
       </c>
       <c r="K79" t="n">
-        <v>0.02082505302908974</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="80">
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.02369655494672001</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.02369655494672001</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="81">
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.02591931949178034</v>
+        <v>0.352197393106352</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.02591931949178034</v>
+        <v>0.352197393106352</v>
       </c>
     </row>
     <row r="82">
@@ -3470,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3610,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3680,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3820,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3855,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
